--- a/data/trans_orig/IP19C02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C02-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43626</t>
+          <t>43548</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38778</t>
+          <t>38764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77247</t>
+          <t>76025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85821</t>
+          <t>85218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21567</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,49 +1091,49 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>16007</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23225</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>9,45%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16007</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10301</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22813</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>47</t>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22445</t>
+          <t>23017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39533</t>
+          <t>40845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206755</t>
+          <t>206832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>218166</t>
+          <t>218553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,44 +1204,44 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>90,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>229716</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>222498</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>235421</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>90,55%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>229716</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>222910</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>235422</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t>95,81%</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434512</t>
+          <t>433200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451600</t>
+          <t>451028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66715</t>
+          <t>67303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73741</t>
+          <t>74194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61400</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69693</t>
+          <t>69609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131526</t>
+          <t>130707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142413</t>
+          <t>141869</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32695</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39392</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>60805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317147</t>
+          <t>316268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>332669</t>
+          <t>332424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>329036</t>
+          <t>329066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>344053</t>
+          <t>344419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651046</t>
+          <t>651856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>673269</t>
+          <t>672842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42165</t>
+          <t>42541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47368</t>
+          <t>47372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82839</t>
+          <t>82915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89626</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>19957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37551</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199355</t>
+          <t>199774</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211651</t>
+          <t>210810</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219099</t>
+          <t>218120</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231725</t>
+          <t>231297</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423093</t>
+          <t>423338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>440280</t>
+          <t>440778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13276</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>75857</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83421</t>
+          <t>83412</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68849</t>
+          <t>69048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78253</t>
+          <t>78731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148600</t>
+          <t>148843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>160185</t>
+          <t>160155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>27968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32379</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56189</t>
+          <t>53864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324298</t>
+          <t>325276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>339465</t>
+          <t>339414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333623</t>
+          <t>334305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349126</t>
+          <t>349312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>663057</t>
+          <t>665382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>684994</t>
+          <t>684738</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14711</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21597</t>
+          <t>21315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38836</t>
+          <t>39032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38074</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57841</t>
+          <t>58575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40178</t>
+          <t>40364</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62511</t>
+          <t>62076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83934</t>
+          <t>83887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112562</t>
+          <t>113648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194899</t>
+          <t>194165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214666</t>
+          <t>214845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189659</t>
+          <t>190094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>211992</t>
+          <t>211806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>392347</t>
+          <t>391261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>420975</t>
+          <t>421022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21718</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>18669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34784</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66022</t>
+          <t>65807</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77836</t>
+          <t>78159</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71041</t>
+          <t>71429</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81652</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140653</t>
+          <t>141257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156560</t>
+          <t>156768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,36%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57080</t>
+          <t>56846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82128</t>
+          <t>81368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59392</t>
+          <t>60081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85650</t>
+          <t>86057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123958</t>
+          <t>124700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159082</t>
+          <t>158533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>280490</t>
+          <t>281250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305538</t>
+          <t>305772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282358</t>
+          <t>281951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>308616</t>
+          <t>307927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>571544</t>
+          <t>572093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>606668</t>
+          <t>605926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>17815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32002</t>
+          <t>31333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22927</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23212</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>39361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67006</t>
+          <t>65861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92520</t>
+          <t>90907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90593</t>
+          <t>89272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126108</t>
+          <t>123846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163547</t>
+          <t>164930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208089</t>
+          <t>210477</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169307</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>194821</t>
+          <t>195966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196907</t>
+          <t>199169</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232422</t>
+          <t>233743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376753</t>
+          <t>374365</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421295</t>
+          <t>419912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,8%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18663</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32935</t>
+          <t>32649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>25791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42699</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47042</t>
+          <t>47537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70104</t>
+          <t>70644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67141</t>
+          <t>67427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81413</t>
+          <t>81239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93246</t>
+          <t>92531</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111812</t>
+          <t>110154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165917</t>
+          <t>165377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188979</t>
+          <t>188484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100387</t>
+          <t>100101</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133507</t>
+          <t>131230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132619</t>
+          <t>131763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173719</t>
+          <t>173549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242682</t>
+          <t>243120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295243</t>
+          <t>295973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258126</t>
+          <t>260403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>291246</t>
+          <t>291532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>310725</t>
+          <t>310895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351825</t>
+          <t>352681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>580833</t>
+          <t>580103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>633394</t>
+          <t>632956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C02-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4193</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6553</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3378</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11250</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11089</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4127</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38698</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>40373</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35676</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>43548</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>35837</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>43535</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>86,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>41537</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38764</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76025</t>
+          <t>76650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85218</t>
+          <t>85380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16007</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9973</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22333</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14827</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9769</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21490</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9536</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21321</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16007</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10302</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23225</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40845</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>229716</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>223390</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>235750</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>320</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>213495</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>206832</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>218553</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>207001</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>218786</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>229716</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>222498</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>235421</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>433200</t>
+          <t>432963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451028</t>
+          <t>451066</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11781</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4361</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1489</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8380</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9255</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6780</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3508</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12117</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66337</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61336</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69704</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>71322</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67303</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74194</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66428</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73835</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>66337</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61000</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69609</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130707</t>
+          <t>131945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141869</t>
+          <t>142455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17335</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33220</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>25741</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18506</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34662</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19209</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34955</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24141</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>17312</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>32665</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39819</t>
+          <t>39954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>337590</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>328511</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>344396</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>483</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>325189</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>316268</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>332424</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>315975</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>331721</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>337590</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>329066</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>344419</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651856</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672842</t>
+          <t>672707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5051</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1951</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5423</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5117</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,07%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1474</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5217</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41489</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37912</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>46013</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42541</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>47372</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42847</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>47374</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,93%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,33%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>98,77%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>41489</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37746</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>123</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82915</t>
+          <t>82641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89592</t>
+          <t>89630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14494</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9278</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22390</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13367</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8921</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19957</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19829</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14494</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9616</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22793</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37306</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>226419</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>218523</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>231635</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>206364</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>199774</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>210810</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>199902</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>211797</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>226419</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>218120</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>231297</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423338</t>
+          <t>422997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>440778</t>
+          <t>440214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>219731</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>219731</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>219731</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7244</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3970</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13140</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5043</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2136</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9691</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2082</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9406</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7244</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3394</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13077</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74881</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>68985</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78155</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80505</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>75857</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83412</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>76142</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>83466</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74881</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>69048</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78731</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148843</t>
+          <t>147987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>160155</t>
+          <t>160055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16688</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32387</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20361</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13830</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27968</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14207</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>28582</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23211</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>16690</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31697</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34508</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53864</t>
+          <t>55641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>342791</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>333615</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>349314</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>332883</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>325276</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>339414</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>324662</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>339037</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>342791</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>334305</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>349312</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665382</t>
+          <t>663605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>684738</t>
+          <t>685482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>503</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>353244</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>353244</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>353244</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10618</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6845</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15269</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5857</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3107</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9753</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9764</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26,45%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10618</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6826</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15216</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,73%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22246</t>
+          <t>22344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17523</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12872</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21296</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>45,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16282</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12386</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19032</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12375</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19242</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>73,55%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17523</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12925</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21315</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>62,27%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39032</t>
+          <t>38950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,47%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50737</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40102</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>62249</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>47545</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>37895</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>58575</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38290</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>59022</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>50737</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>40364</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>62076</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,12%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83887</t>
+          <t>84504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113648</t>
+          <t>112894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>201433</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>189921</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212068</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,1%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205195</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>194165</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>214845</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>193718</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>81,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>201433</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>190094</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>211806</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>79,88%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391261</t>
+          <t>392015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421022</t>
+          <t>420405</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10584</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6209</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16700</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>15377</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9581</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21933</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22338</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10584</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6318</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16269</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>34574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77114</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70998</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81489</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,96%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72363</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65807</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78159</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>65402</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>77636</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77114</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71429</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>81380</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141257</t>
+          <t>140863</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156768</t>
+          <t>156791</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58586</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>84759</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>68778</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>56846</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>81368</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>57202</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>81714</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>71938</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>60081</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>86057</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124700</t>
+          <t>122953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158533</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>296070</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>283249</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>309422</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>426</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>293840</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>281250</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>305772</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>280904</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>305416</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>81,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>296070</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>281951</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>307927</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>572093</t>
+          <t>572469</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>605926</t>
+          <t>607673</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11947</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16531</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11731</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5802</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17815</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39,46%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23398</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31333</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>58,69%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12343</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7759</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16781</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50,81%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,09%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17999</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11915</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23928</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>60,54%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17958</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39361</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>108741</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>91046</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>127120</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>79289</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>65861</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>90907</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>107227</t>
+          <t>86200</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89272</t>
+          <t>71143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123846</t>
+          <t>99396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>186516</t>
+          <t>194941</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164930</t>
+          <t>172607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210477</t>
+          <t>216364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>200804</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>182425</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>218499</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>182538</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>170920</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>195966</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>215788</t>
+          <t>179852</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199169</t>
+          <t>166656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>233743</t>
+          <t>194909</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>398326</t>
+          <t>380656</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>374365</t>
+          <t>359233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>419912</t>
+          <t>402990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>70,01%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34758</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25941</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44491</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25319</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18837</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32649</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33617</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
+          <t>34754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>58936</t>
+          <t>61671</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47537</t>
+          <t>49798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70644</t>
+          <t>73125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92502</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>82769</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101319</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>72,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>65,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>79,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>74757</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67427</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>81239</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>74,7%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,18%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102328</t>
+          <t>76671</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92531</t>
+          <t>68829</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110154</t>
+          <t>83365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>177085</t>
+          <t>169171</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165377</t>
+          <t>157717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188484</t>
+          <t>181044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>155447</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>135027</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>174902</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>116339</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>131230</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131763</t>
+          <t>106109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173549</t>
+          <t>139724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>268849</t>
+          <t>279704</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>243120</t>
+          <t>254485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295973</t>
+          <t>306859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>305648</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>286193</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>326068</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>70,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>389</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>275294</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>260403</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>291532</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>331934</t>
+          <t>272020</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>310895</t>
+          <t>256554</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352681</t>
+          <t>290169</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>607227</t>
+          <t>577668</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>580103</t>
+          <t>550513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632956</t>
+          <t>602887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
